--- a/erp-server/erp-server-file/src/main/resources/excel/wms/pickingLists.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/pickingLists.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>拣货单号</t>
   </si>
@@ -52,6 +52,9 @@
     <t>数量</t>
   </si>
   <si>
+    <t>打印状态</t>
+  </si>
+  <si>
     <t>存放库区</t>
   </si>
   <si>
@@ -61,9 +64,15 @@
     <t>更新人</t>
   </si>
   <si>
+    <t>打印人</t>
+  </si>
+  <si>
     <t>更新时间</t>
   </si>
   <si>
+    <t>打印时间</t>
+  </si>
+  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -85,6 +94,9 @@
     <t>{.qty}</t>
   </si>
   <si>
+    <t>{.printStatusName}</t>
+  </si>
+  <si>
     <t>{.stagingAreaName}</t>
   </si>
   <si>
@@ -94,7 +106,13 @@
     <t>{.updateUserName}</t>
   </si>
   <si>
+    <t>{.printUserName}</t>
+  </si>
+  <si>
     <t>{.updateTime}</t>
+  </si>
+  <si>
+    <t>{.printTime}</t>
   </si>
 </sst>
 </file>
@@ -1112,7 +1130,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.125" customWidth="1"/>
@@ -1120,28 +1138,29 @@
     <col min="3" max="3" width="27.375" customWidth="1"/>
     <col min="4" max="4" width="20.5" customWidth="1"/>
     <col min="5" max="6" width="20.75" customWidth="1"/>
-    <col min="7" max="8" width="13.875" customWidth="1"/>
-    <col min="9" max="9" width="18.5" customWidth="1"/>
-    <col min="10" max="10" width="12.625" customWidth="1"/>
-    <col min="11" max="11" width="42" customWidth="1"/>
-    <col min="12" max="12" width="14.375" customWidth="1"/>
-    <col min="13" max="13" width="13.125" customWidth="1"/>
-    <col min="14" max="14" width="10.25" customWidth="1"/>
-    <col min="15" max="15" width="26.75" customWidth="1"/>
-    <col min="16" max="16" width="27.375" customWidth="1"/>
-    <col min="17" max="17" width="28" customWidth="1"/>
-    <col min="18" max="18" width="10.5" customWidth="1"/>
-    <col min="19" max="19" width="21.25" customWidth="1"/>
-    <col min="20" max="20" width="10.625" customWidth="1"/>
-    <col min="21" max="21" width="22.25" customWidth="1"/>
-    <col min="22" max="22" width="8.875" customWidth="1"/>
-    <col min="23" max="23" width="31.25" customWidth="1"/>
-    <col min="25" max="25" width="17.25" customWidth="1"/>
-    <col min="27" max="27" width="9.375" customWidth="1"/>
-    <col min="28" max="28" width="14.375" customWidth="1"/>
+    <col min="7" max="9" width="13.875" customWidth="1"/>
+    <col min="10" max="10" width="18.5" customWidth="1"/>
+    <col min="11" max="12" width="12.625" customWidth="1"/>
+    <col min="13" max="13" width="24.625" customWidth="1"/>
+    <col min="14" max="14" width="22.5" customWidth="1"/>
+    <col min="15" max="15" width="14.375" customWidth="1"/>
+    <col min="16" max="16" width="13.125" customWidth="1"/>
+    <col min="17" max="17" width="10.25" customWidth="1"/>
+    <col min="18" max="18" width="26.75" customWidth="1"/>
+    <col min="19" max="19" width="27.375" customWidth="1"/>
+    <col min="20" max="20" width="28" customWidth="1"/>
+    <col min="21" max="21" width="10.5" customWidth="1"/>
+    <col min="22" max="22" width="21.25" customWidth="1"/>
+    <col min="23" max="23" width="10.625" customWidth="1"/>
+    <col min="24" max="24" width="22.25" customWidth="1"/>
+    <col min="25" max="25" width="8.875" customWidth="1"/>
+    <col min="26" max="26" width="31.25" customWidth="1"/>
+    <col min="28" max="28" width="17.25" customWidth="1"/>
+    <col min="30" max="30" width="9.375" customWidth="1"/>
+    <col min="31" max="31" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:21">
+    <row r="1" s="1" customFormat="1" spans="1:24">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1175,9 +1194,15 @@
       <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1"/>
-      <c r="M1"/>
-      <c r="N1"/>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="O1"/>
       <c r="P1"/>
       <c r="Q1"/>
@@ -1185,44 +1210,53 @@
       <c r="S1"/>
       <c r="T1"/>
       <c r="U1"/>
+      <c r="V1"/>
+      <c r="W1"/>
+      <c r="X1"/>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:21">
+    <row r="2" s="2" customFormat="1" spans="1:24">
       <c r="A2" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
@@ -1230,6 +1264,9 @@
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
